--- a/artfynd/A 438-2022 artfynd.xlsx
+++ b/artfynd/A 438-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 438-2022 artfynd.xlsx
+++ b/artfynd/A 438-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY38"/>
+  <dimension ref="A1:AY39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>100577340</v>
+        <v>102575855</v>
       </c>
       <c r="B2" t="n">
-        <v>78570</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83299</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,35 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2081</v>
+        <v>308</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Svensberg V, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>447245.9319596914</v>
+        <v>447233</v>
       </c>
       <c r="R2" t="n">
-        <v>7034266.600240049</v>
+        <v>7034286</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -746,22 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2022-05-07</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-07-30</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2022-05-07</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-07-30</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -788,15 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>100580330</v>
+        <v>100581144</v>
       </c>
       <c r="B3" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -804,41 +783,35 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Svensberg V, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>447094.5440095781</v>
+        <v>447001</v>
       </c>
       <c r="R3" t="n">
-        <v>7034059.105307313</v>
+        <v>7033974</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -868,24 +841,9 @@
           <t>2022-05-07</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2022-05-07</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -912,15 +870,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>100580836</v>
+        <v>102575818</v>
       </c>
       <c r="B4" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -928,35 +881,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Svensberg V, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>447098.8154083307</v>
+        <v>447247</v>
       </c>
       <c r="R4" t="n">
-        <v>7034019.182838603</v>
+        <v>7034250</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -983,22 +935,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2022-05-07</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-07-30</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2022-05-07</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-07-30</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1025,15 +967,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>100577370</v>
+        <v>102575842</v>
       </c>
       <c r="B5" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1041,35 +978,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Svensberg V, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>447245.9319596914</v>
+        <v>447177</v>
       </c>
       <c r="R5" t="n">
-        <v>7034266.600240049</v>
+        <v>7034140</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1096,22 +1032,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2022-05-07</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-07-30</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2022-05-07</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-07-30</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1138,15 +1064,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>100578737</v>
+        <v>102575851</v>
       </c>
       <c r="B6" t="n">
-        <v>78570</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1154,35 +1075,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2081</v>
+        <v>1312</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Svensberg V, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>447177.9397922915</v>
+        <v>447217</v>
       </c>
       <c r="R6" t="n">
-        <v>7034248.918050246</v>
+        <v>7034254</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1209,22 +1129,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2022-05-07</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-07-30</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2022-05-07</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-07-30</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1251,51 +1161,48 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>100578729</v>
+        <v>102575817</v>
       </c>
       <c r="B7" t="n">
-        <v>78596</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92281</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6462</v>
+        <v>2062</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Svensberg V, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>447177.9397922915</v>
+        <v>447247</v>
       </c>
       <c r="R7" t="n">
-        <v>7034248.918050246</v>
+        <v>7034250</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1322,22 +1229,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2022-05-07</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-07-30</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2022-05-07</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-07-30</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1346,6 +1243,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1364,15 +1262,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>100580031</v>
+        <v>100577340</v>
       </c>
       <c r="B8" t="n">
-        <v>73693</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1380,21 +1273,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6440</v>
+        <v>2081</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1405,10 +1298,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>447101.8456152279</v>
+        <v>447246</v>
       </c>
       <c r="R8" t="n">
-        <v>7034093.910329391</v>
+        <v>7034267</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1438,19 +1331,9 @@
           <t>2022-05-07</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2022-05-07</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1477,37 +1360,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>100578725</v>
+        <v>100578737</v>
       </c>
       <c r="B9" t="n">
-        <v>78527</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>229497</v>
+        <v>2081</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1518,10 +1396,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>447177.9397922915</v>
+        <v>447178</v>
       </c>
       <c r="R9" t="n">
-        <v>7034248.918050246</v>
+        <v>7034249</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1551,24 +1429,9 @@
           <t>2022-05-07</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2022-05-07</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>På sälg.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1595,51 +1458,45 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>100578812</v>
+        <v>102575831</v>
       </c>
       <c r="B10" t="n">
-        <v>78533</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>229748</v>
+        <v>2081</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Gytterlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Protopannaria pezizoides</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Svensberg V, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>447177.9397922915</v>
+        <v>447256</v>
       </c>
       <c r="R10" t="n">
-        <v>7034248.918050246</v>
+        <v>7034361</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1666,22 +1523,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2022-05-07</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-07-30</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2022-05-07</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-07-30</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1708,51 +1555,45 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>100577357</v>
+        <v>102575856</v>
       </c>
       <c r="B11" t="n">
-        <v>78596</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6462</v>
+        <v>2081</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Svensberg V, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>447245.9319596914</v>
+        <v>447233</v>
       </c>
       <c r="R11" t="n">
-        <v>7034266.600240049</v>
+        <v>7034286</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1779,22 +1620,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2022-05-07</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-07-30</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2022-05-07</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-07-30</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1821,37 +1652,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>102575844</v>
+        <v>102575816</v>
       </c>
       <c r="B12" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1861,10 +1687,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>447177.4868617271</v>
+        <v>447247</v>
       </c>
       <c r="R12" t="n">
-        <v>7034140.122132287</v>
+        <v>7034250</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1894,19 +1720,9 @@
           <t>2022-07-30</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2022-07-30</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1933,65 +1749,48 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>102575819</v>
+        <v>112213247</v>
       </c>
       <c r="B13" t="n">
-        <v>56540</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91435</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>103021</v>
+        <v>5747</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Ramaria safraniolens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr"/>
+          <t>Christan</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Svensberg V, Jmt</t>
+          <t>Ol-olssvarttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>447110.1737983227</v>
+        <v>447156</v>
       </c>
       <c r="R13" t="n">
-        <v>7034001.083809691</v>
+        <v>7034283</v>
       </c>
       <c r="S13" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2015,27 +1814,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2022-07-30</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-09-19</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2022-07-30</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Min antal. Hördes.</t>
+          <t>2023-09-19</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2050,31 +1834,26 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Erik Lundmark</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Erik Lundmark</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>102575824</v>
+        <v>100577370</v>
       </c>
       <c r="B14" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
@@ -2096,16 +1875,17 @@
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Svensberg V, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>447052.1926755086</v>
+        <v>447246</v>
       </c>
       <c r="R14" t="n">
-        <v>7033992.640346262</v>
+        <v>7034267</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2132,22 +1912,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2022-07-30</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-05-07</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2022-07-30</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-05-07</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2174,37 +1944,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>102575831</v>
+        <v>102575814</v>
       </c>
       <c r="B15" t="n">
-        <v>78570</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2214,10 +1979,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>447255.5585893725</v>
+        <v>447268</v>
       </c>
       <c r="R15" t="n">
-        <v>7034360.913150411</v>
+        <v>7034297</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2247,19 +2012,9 @@
           <t>2022-07-30</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2022-07-30</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2286,37 +2041,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>102575856</v>
+        <v>102575824</v>
       </c>
       <c r="B16" t="n">
-        <v>78570</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2326,10 +2076,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>447232.3474698417</v>
+        <v>447052</v>
       </c>
       <c r="R16" t="n">
-        <v>7034285.629522036</v>
+        <v>7033992</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2359,19 +2109,9 @@
           <t>2022-07-30</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2022-07-30</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2398,37 +2138,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>102575849</v>
+        <v>102575828</v>
       </c>
       <c r="B17" t="n">
-        <v>96354</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2438,10 +2173,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>447217.0387923816</v>
+        <v>447210</v>
       </c>
       <c r="R17" t="n">
-        <v>7034254.540511679</v>
+        <v>7034184</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2471,19 +2206,9 @@
           <t>2022-07-30</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2022-07-30</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2510,37 +2235,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>102575859</v>
+        <v>102575844</v>
       </c>
       <c r="B18" t="n">
-        <v>96251</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>219790</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2550,10 +2270,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>447232.3474698417</v>
+        <v>447177</v>
       </c>
       <c r="R18" t="n">
-        <v>7034285.629522036</v>
+        <v>7034140</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2583,19 +2303,9 @@
           <t>2022-07-30</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2022-07-30</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2622,19 +2332,14 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>102575828</v>
+        <v>102575850</v>
       </c>
       <c r="B19" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
@@ -2662,10 +2367,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>447209.6029472441</v>
+        <v>447217</v>
       </c>
       <c r="R19" t="n">
-        <v>7034184.367043618</v>
+        <v>7034254</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2695,19 +2400,9 @@
           <t>2022-07-30</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2022-07-30</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2734,50 +2429,46 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>102575829</v>
+        <v>100580031</v>
       </c>
       <c r="B20" t="n">
-        <v>96354</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83307</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>221952</v>
+        <v>6440</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Svensberg V, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>447209.6029472441</v>
+        <v>447102</v>
       </c>
       <c r="R20" t="n">
-        <v>7034184.367043618</v>
+        <v>7034094</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2804,22 +2495,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2022-07-30</t>
-        </is>
-      </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-05-07</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2022-07-30</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-05-07</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2846,15 +2527,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>102575855</v>
+        <v>102575815</v>
       </c>
       <c r="B21" t="n">
-        <v>73686</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83307</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2862,21 +2538,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>308</v>
+        <v>6440</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2886,10 +2562,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>447232.3474698417</v>
+        <v>447268</v>
       </c>
       <c r="R21" t="n">
-        <v>7034285.629522036</v>
+        <v>7034297</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2919,19 +2595,9 @@
           <t>2022-07-30</t>
         </is>
       </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2022-07-30</t>
-        </is>
-      </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2958,15 +2624,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>102575851</v>
+        <v>102575827</v>
       </c>
       <c r="B22" t="n">
-        <v>81236</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83307</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2974,21 +2635,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1312</v>
+        <v>6440</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2998,10 +2659,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>447217.0387923816</v>
+        <v>447210</v>
       </c>
       <c r="R22" t="n">
-        <v>7034254.540511679</v>
+        <v>7034184</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -3031,19 +2692,9 @@
           <t>2022-07-30</t>
         </is>
       </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2022-07-30</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3070,50 +2721,46 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>102575827</v>
+        <v>100577357</v>
       </c>
       <c r="B23" t="n">
-        <v>73693</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6440</v>
+        <v>6462</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Svensberg V, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>447209.6029472441</v>
+        <v>447246</v>
       </c>
       <c r="R23" t="n">
-        <v>7034184.367043618</v>
+        <v>7034267</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3140,22 +2787,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2022-07-30</t>
-        </is>
-      </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-05-07</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2022-07-30</t>
-        </is>
-      </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-05-07</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3182,50 +2819,46 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>102575814</v>
+        <v>100578729</v>
       </c>
       <c r="B24" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Svensberg V, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>447268.404390368</v>
+        <v>447178</v>
       </c>
       <c r="R24" t="n">
-        <v>7034297.123323589</v>
+        <v>7034249</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3252,22 +2885,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2022-07-30</t>
-        </is>
-      </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-05-07</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2022-07-30</t>
-        </is>
-      </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-05-07</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3294,50 +2917,52 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>102575812</v>
+        <v>100580330</v>
       </c>
       <c r="B25" t="n">
-        <v>103250</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>221725</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Svensberg V, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>447207.2859999727</v>
+        <v>447095</v>
       </c>
       <c r="R25" t="n">
-        <v>7034234.105386307</v>
+        <v>7034059</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3364,22 +2989,17 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2022-07-30</t>
-        </is>
-      </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-05-07</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2022-07-30</t>
-        </is>
-      </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-05-07</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3406,50 +3026,57 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>102575815</v>
+        <v>102575846</v>
       </c>
       <c r="B26" t="n">
-        <v>73693</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57132</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6440</v>
+        <v>102612</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Svensberg V, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>447268.404390368</v>
+        <v>447177</v>
       </c>
       <c r="R26" t="n">
-        <v>7034297.123323589</v>
+        <v>7034140</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3479,19 +3106,14 @@
           <t>2022-07-30</t>
         </is>
       </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2022-07-30</t>
         </is>
       </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>00:00</t>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Uppflog.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3518,50 +3140,57 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>102575816</v>
+        <v>102575819</v>
       </c>
       <c r="B27" t="n">
-        <v>89356</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5447</v>
+        <v>103021</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Svensberg V, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>447247.0032705484</v>
+        <v>447110</v>
       </c>
       <c r="R27" t="n">
-        <v>7034250.016127262</v>
+        <v>7034001</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3591,19 +3220,14 @@
           <t>2022-07-30</t>
         </is>
       </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2022-07-30</t>
         </is>
       </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>00:00</t>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Min antal. Hördes.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3630,15 +3254,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>102575843</v>
+        <v>102575859</v>
       </c>
       <c r="B28" t="n">
-        <v>96354</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99035</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3646,21 +3265,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>221952</v>
+        <v>219790</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3670,10 +3289,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>447177.4868617271</v>
+        <v>447233</v>
       </c>
       <c r="R28" t="n">
-        <v>7034140.122132287</v>
+        <v>7034286</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3703,19 +3322,9 @@
           <t>2022-07-30</t>
         </is>
       </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2022-07-30</t>
-        </is>
-      </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3742,15 +3351,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>102575813</v>
+        <v>102575812</v>
       </c>
       <c r="B29" t="n">
-        <v>96354</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106229</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3758,21 +3362,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>221952</v>
+        <v>221725</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3782,10 +3386,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>447268.404390368</v>
+        <v>447207</v>
       </c>
       <c r="R29" t="n">
-        <v>7034297.123323589</v>
+        <v>7034234</v>
       </c>
       <c r="S29" t="n">
         <v>25</v>
@@ -3815,19 +3419,9 @@
           <t>2022-07-30</t>
         </is>
       </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2022-07-30</t>
-        </is>
-      </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3854,37 +3448,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>102575842</v>
+        <v>102575813</v>
       </c>
       <c r="B30" t="n">
-        <v>81236</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99140</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1312</v>
+        <v>221952</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3894,10 +3483,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>447177.4868617271</v>
+        <v>447268</v>
       </c>
       <c r="R30" t="n">
-        <v>7034140.122132287</v>
+        <v>7034297</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -3927,19 +3516,9 @@
           <t>2022-07-30</t>
         </is>
       </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2022-07-30</t>
-        </is>
-      </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3966,37 +3545,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>102575850</v>
+        <v>102575825</v>
       </c>
       <c r="B31" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99140</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -4006,10 +3580,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>447217.0387923816</v>
+        <v>447052</v>
       </c>
       <c r="R31" t="n">
-        <v>7034254.540511679</v>
+        <v>7033992</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -4039,19 +3613,9 @@
           <t>2022-07-30</t>
         </is>
       </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2022-07-30</t>
-        </is>
-      </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4078,15 +3642,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>102575825</v>
+        <v>102575826</v>
       </c>
       <c r="B32" t="n">
-        <v>96354</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99140</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4118,10 +3677,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>447052.1926755086</v>
+        <v>447166</v>
       </c>
       <c r="R32" t="n">
-        <v>7033992.640346262</v>
+        <v>7034059</v>
       </c>
       <c r="S32" t="n">
         <v>25</v>
@@ -4151,19 +3710,9 @@
           <t>2022-07-30</t>
         </is>
       </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2022-07-30</t>
-        </is>
-      </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4190,15 +3739,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>102575858</v>
+        <v>102575829</v>
       </c>
       <c r="B33" t="n">
-        <v>96354</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99140</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4230,10 +3774,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>447232.3474698417</v>
+        <v>447210</v>
       </c>
       <c r="R33" t="n">
-        <v>7034285.629522036</v>
+        <v>7034184</v>
       </c>
       <c r="S33" t="n">
         <v>25</v>
@@ -4263,19 +3807,9 @@
           <t>2022-07-30</t>
         </is>
       </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2022-07-30</t>
-        </is>
-      </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4302,37 +3836,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>102575818</v>
+        <v>102575830</v>
       </c>
       <c r="B34" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99140</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1202</v>
+        <v>221952</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4342,10 +3871,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>447247.0032705484</v>
+        <v>447315</v>
       </c>
       <c r="R34" t="n">
-        <v>7034250.016127262</v>
+        <v>7034365</v>
       </c>
       <c r="S34" t="n">
         <v>25</v>
@@ -4375,19 +3904,9 @@
           <t>2022-07-30</t>
         </is>
       </c>
-      <c r="Z34" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2022-07-30</t>
-        </is>
-      </c>
-      <c r="AB34" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4414,62 +3933,45 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>102575846</v>
+        <v>102575843</v>
       </c>
       <c r="B35" t="n">
-        <v>55608</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99140</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>102612</v>
+        <v>221952</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
-      <c r="N35" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Svensberg V, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>447177.4868617271</v>
+        <v>447177</v>
       </c>
       <c r="R35" t="n">
-        <v>7034140.122132287</v>
+        <v>7034140</v>
       </c>
       <c r="S35" t="n">
         <v>25</v>
@@ -4499,24 +4001,9 @@
           <t>2022-07-30</t>
         </is>
       </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>2022-07-30</t>
-        </is>
-      </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Uppflog.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4543,56 +4030,48 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>112873512</v>
+        <v>102575849</v>
       </c>
       <c r="B36" t="n">
-        <v>89944</v>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99140</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1202</v>
+        <v>221952</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
-      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Tjärnhön, Alsen, Jmt</t>
+          <t>Svensberg V, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>447071</v>
+        <v>447217</v>
       </c>
       <c r="R36" t="n">
-        <v>7034002</v>
+        <v>7034254</v>
       </c>
       <c r="S36" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4616,12 +4095,12 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2023-10-13</t>
+          <t>2022-07-30</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2023-10-13</t>
+          <t>2022-07-30</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4630,75 +4109,66 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
-      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Rashid Kadhim</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Rashid Kadhim</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>112873506</v>
+        <v>102575858</v>
       </c>
       <c r="B37" t="n">
-        <v>90284</v>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99140</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>2062</v>
+        <v>221952</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
-      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Tjärnhön, Alsen, Jmt</t>
+          <t>Svensberg V, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>447071</v>
+        <v>447233</v>
       </c>
       <c r="R37" t="n">
-        <v>7034002</v>
+        <v>7034286</v>
       </c>
       <c r="S37" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4722,12 +4192,12 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2023-10-13</t>
+          <t>2022-07-30</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2023-10-13</t>
+          <t>2022-07-30</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4736,72 +4206,64 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
-      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Rashid Kadhim</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Rashid Kadhim</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>102575817</v>
+        <v>100578725</v>
       </c>
       <c r="B38" t="n">
-        <v>90369</v>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80392</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>2062</v>
+        <v>229497</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr"/>
-      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Svensberg V, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>447247</v>
+        <v>447178</v>
       </c>
       <c r="R38" t="n">
-        <v>7034250</v>
+        <v>7034249</v>
       </c>
       <c r="S38" t="n">
         <v>25</v>
@@ -4828,12 +4290,17 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2022-07-30</t>
+          <t>2022-05-07</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2022-07-30</t>
+          <t>2022-05-07</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>På sälg.</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4842,7 +4309,6 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
-      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -4858,6 +4324,104 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>100578812</v>
+      </c>
+      <c r="B39" t="n">
+        <v>80398</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>229748</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Gytterlav</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Protopannaria pezizoides</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Svensberg V, Jmt</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>447178</v>
+      </c>
+      <c r="R39" t="n">
+        <v>7034249</v>
+      </c>
+      <c r="S39" t="n">
+        <v>25</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2022-05-07</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2022-05-07</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Johan Råghall</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Johan Råghall</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 438-2022 artfynd.xlsx
+++ b/artfynd/A 438-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY39"/>
+  <dimension ref="A1:AZ39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102575855</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -867,6 +877,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100581144</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -964,6 +979,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102575818</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1061,6 +1081,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102575842</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1158,6 +1183,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102575851</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1259,6 +1289,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102575817</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1357,6 +1392,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100577340</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1455,6 +1495,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100578737</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1552,6 +1597,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102575831</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1649,6 +1699,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102575856</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1746,6 +1801,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102575816</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1843,6 +1903,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112213247</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1941,6 +2006,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100577370</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2038,6 +2108,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102575814</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2135,6 +2210,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102575824</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2232,6 +2312,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102575828</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2329,6 +2414,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102575844</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2426,6 +2516,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102575850</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2524,6 +2619,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100580031</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2621,6 +2721,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102575815</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2718,6 +2823,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102575827</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2816,6 +2926,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100577357</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2914,6 +3029,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100578729</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3023,6 +3143,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100580330</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3137,6 +3262,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102575846</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3251,6 +3381,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102575819</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3348,6 +3483,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102575859</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3445,6 +3585,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102575812</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3542,6 +3687,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102575813</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3639,6 +3789,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102575825</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3736,6 +3891,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102575826</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3833,6 +3993,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102575829</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -3930,6 +4095,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102575830</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4027,6 +4197,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102575843</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4124,6 +4299,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102575849</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4221,6 +4401,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102575858</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4324,6 +4509,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100578725</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4422,8 +4612,53 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100578812</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>